--- a/1-LATEX/2-DADOS/3-OUTPUT/moderadores_significativos.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/moderadores_significativos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,22 +389,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoAgroforestry assessment</t>
+          <t>Tipo_IntervencaoAgrobiodiversity management</t>
         </is>
       </c>
       <c r="C2">
-        <v>-0.5805234566547032</v>
+        <v>-0.4054659999999774</v>
       </c>
       <c r="D2">
-        <v>0.1321737087236022</v>
+        <v>6.115083852010249E-07</v>
       </c>
       <c r="E2">
-        <v>0.06030420674827358</v>
+        <v>8.680391833861374E-14</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -413,22 +413,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoEthnobotanical survey</t>
+          <t>Tipo_IntervencaoAgroforestry management</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.06139175200120005</v>
+        <v>-0.4054659999999934</v>
       </c>
       <c r="D3">
-        <v>2.876924738835152E-08</v>
+        <v>3.122510020863939E-07</v>
       </c>
       <c r="E3">
-        <v>2.983311458912115E-07</v>
+        <v>3.263841912061384E-11</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -437,22 +437,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoHome garden knowledge transmission</t>
+          <t>Tipo_IntervencaoBiocultural landscape assessment</t>
         </is>
       </c>
       <c r="C4">
-        <v>-0.7834498549370886</v>
+        <v>-0.405465999999975</v>
       </c>
       <c r="D4">
-        <v>0.1478147896876738</v>
+        <v>3.254507534498555E-07</v>
       </c>
       <c r="E4">
-        <v>0.01930950038835454</v>
+        <v>2.717361337416577E-15</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -461,22 +461,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoOn-farm conservation</t>
+          <t>Tipo_IntervencaoClimate adaptation assessment</t>
         </is>
       </c>
       <c r="C5">
-        <v>-0.1811274908058922</v>
+        <v>0.187521000000013</v>
       </c>
       <c r="D5">
-        <v>0.01470912820592961</v>
+        <v>3.00431625549127E-07</v>
       </c>
       <c r="E5">
-        <v>0.04843754543033569</v>
+        <v>1.019942902762066E-06</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -485,22 +485,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoSacred grove conservation</t>
+          <t>Tipo_IntervencaoEcological knowledge indicator</t>
         </is>
       </c>
       <c r="C6">
-        <v>-0.6579443245010178</v>
+        <v>0.4385040000000171</v>
       </c>
       <c r="D6">
-        <v>0.1478147896876638</v>
+        <v>1.642390193186067E-07</v>
       </c>
       <c r="E6">
-        <v>0.02917668727687919</v>
+        <v>8.833428464486455E-12</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -509,22 +509,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
+          <t>Tipo_IntervencaoEthnobotanical assessment</t>
         </is>
       </c>
       <c r="C7">
-        <v>0.4249205554697837</v>
+        <v>-0.4054659999999866</v>
       </c>
       <c r="D7">
-        <v>0.1139127490316687</v>
+        <v>4.425288257921226E-07</v>
       </c>
       <c r="E7">
-        <v>0.05354888131605116</v>
+        <v>2.360330899936472E-14</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -533,22 +533,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
+          <t>Tipo_IntervencaoFarmer perception survey</t>
         </is>
       </c>
       <c r="C8">
-        <v>0.6861732307691261</v>
+        <v>-0.06924485538102444</v>
       </c>
       <c r="D8">
-        <v>0.1871381538463709</v>
+        <v>4.104890638389102E-07</v>
       </c>
       <c r="E8">
-        <v>0.0570696876793429</v>
+        <v>6.881655969223174E-07</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -557,22 +557,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RegiaoAsia</t>
+          <t>Tipo_IntervencaoHerbal knowledge assessment</t>
         </is>
       </c>
       <c r="C9">
-        <v>-0.4054660000000546</v>
+        <v>-0.4054659999999813</v>
       </c>
       <c r="D9">
-        <v>2.584048253340671E-08</v>
+        <v>2.999993676152833E-07</v>
       </c>
       <c r="E9">
-        <v>5.745356827824759E-10</v>
+        <v>6.052508814561567E-12</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -581,22 +581,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoAgroforestry assessment</t>
+          <t>Tipo_IntervencaoIndigenous knowledge transmission</t>
         </is>
       </c>
       <c r="C10">
-        <v>-0.6730030013415873</v>
+        <v>-0.1823219999999864</v>
       </c>
       <c r="D10">
-        <v>0.1318290078775098</v>
+        <v>3.023132631770765E-07</v>
       </c>
       <c r="E10">
-        <v>0.06204885723009985</v>
+        <v>3.700355875901586E-16</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -605,22 +605,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoAgroforestry management</t>
+          <t>Tipo_IntervencaoIndigenous storytelling review</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.4054659999999092</v>
+        <v>-0.1823219999999826</v>
       </c>
       <c r="D11">
-        <v>2.94090677874457E-08</v>
+        <v>1.995990256282826E-07</v>
       </c>
       <c r="E11">
-        <v>4.617500367563914E-08</v>
+        <v>6.969465355811678E-07</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -629,22 +629,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoClimate adaptation assessment</t>
+          <t>Tipo_IntervencaoPost-disaster food security</t>
         </is>
       </c>
       <c r="C12">
-        <v>0.6372849999998229</v>
+        <v>0.3342520366768659</v>
       </c>
       <c r="D12">
-        <v>5.745524780300012E-08</v>
+        <v>3.004316255491266E-07</v>
       </c>
       <c r="E12">
-        <v>2.811441412033505E-09</v>
+        <v>1.913539329751795E-12</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -653,22 +653,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoEcological knowledge indicator</t>
+          <t>Tipo_IntervencaoSeed network analysis</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.918328999999891</v>
+        <v>-0.405465999999988</v>
       </c>
       <c r="D13">
-        <v>2.432630424441328E-08</v>
+        <v>5.350035389529029E-07</v>
       </c>
       <c r="E13">
-        <v>1.686389765605374E-08</v>
+        <v>6.113107233712592E-16</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -677,22 +677,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoEthnobotanical survey</t>
+          <t>Tipo_IntervencaoSeed system assessment</t>
         </is>
       </c>
       <c r="C14">
-        <v>0.405465999999868</v>
+        <v>-1.098612999999981</v>
       </c>
       <c r="D14">
-        <v>4.135642362796381E-08</v>
+        <v>3.047012385148154E-07</v>
       </c>
       <c r="E14">
-        <v>6.493347653297616E-08</v>
+        <v>2.931407337507796E-23</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -701,22 +701,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoHerbal knowledge assessment</t>
+          <t>Tipo_IntervencaoSoil conservation assessment</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.2231439999998313</v>
+        <v>-0.6683479999999757</v>
       </c>
       <c r="D15">
-        <v>7.827120062408931E-08</v>
+        <v>3.036151684149451E-07</v>
       </c>
       <c r="E15">
-        <v>2.233042068089432E-07</v>
+        <v>7.217932678980618E-14</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -725,22 +725,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoLand sharing assessment</t>
+          <t>Tipo_IntervencaoTraditional beekeeping</t>
         </is>
       </c>
       <c r="C16">
-        <v>0.4054659999998255</v>
+        <v>-0.4054659999999765</v>
       </c>
       <c r="D16">
-        <v>5.883993276410134E-08</v>
+        <v>1.713757595516729E-07</v>
       </c>
       <c r="E16">
-        <v>9.238423098937396E-08</v>
+        <v>6.513079902605721E-14</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -749,46 +749,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoOn-farm conservation</t>
+          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
         </is>
       </c>
       <c r="C17">
-        <v>0.2300726179613616</v>
+        <v>1.053977851873704</v>
       </c>
       <c r="D17">
-        <v>0.03486020276917905</v>
+        <v>0.4591699806279946</v>
       </c>
       <c r="E17">
-        <v>0.05500264321803607</v>
+        <v>0.09986839441749908</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoPost-disaster food security</t>
+          <t>Tipo_IntervencaoAgrobiodiversity assessment</t>
         </is>
       </c>
       <c r="C18">
-        <v>0.2529969631494836</v>
+        <v>-0.4054659999999681</v>
       </c>
       <c r="D18">
-        <v>5.52373885623986E-08</v>
+        <v>4.62910055762686E-08</v>
       </c>
       <c r="E18">
-        <v>1.389946080574821E-07</v>
+        <v>7.268123451197136E-08</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -797,22 +797,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoSeed system assessment</t>
+          <t>Tipo_IntervencaoAgroforestry assessment</t>
         </is>
       </c>
       <c r="C19">
-        <v>0.3553099975856345</v>
+        <v>-1.078469001341468</v>
       </c>
       <c r="D19">
-        <v>1.652646937294957E-08</v>
+        <v>0.1318290078774778</v>
       </c>
       <c r="E19">
-        <v>2.961097982526057E-08</v>
+        <v>0.07451256790378014</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -821,22 +821,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoSoil conservation assessment</t>
+          <t>Tipo_IntervencaoEcological knowledge indicator</t>
         </is>
       </c>
       <c r="C20">
-        <v>-0.3210950000001806</v>
+        <v>0.5128630000000222</v>
       </c>
       <c r="D20">
-        <v>5.941732689348842E-08</v>
+        <v>5.496139319745887E-08</v>
       </c>
       <c r="E20">
-        <v>1.178039057647027E-07</v>
+        <v>3.083310830628834E-15</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -845,22 +845,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional beekeeping</t>
+          <t>Tipo_IntervencaoEthnobotanical assessment</t>
         </is>
       </c>
       <c r="C21">
-        <v>0.4054659999999004</v>
+        <v>-0.4054659999999822</v>
       </c>
       <c r="D21">
-        <v>1.168597856272471E-08</v>
+        <v>3.983165853266648E-08</v>
       </c>
       <c r="E21">
-        <v>1.834808593686665E-08</v>
+        <v>2.106852915522585E-18</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -869,22 +869,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional flood knowledge</t>
+          <t>Tipo_IntervencaoFarmer perception survey</t>
         </is>
       </c>
       <c r="C22">
-        <v>0.7529464996245339</v>
+        <v>-0.4054659999999313</v>
       </c>
       <c r="D22">
-        <v>0.2101168056175254</v>
+        <v>5.662759855051244E-09</v>
       </c>
       <c r="E22">
-        <v>0.07848705633388674</v>
+        <v>2.165282347606011E-12</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -893,22 +893,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
+          <t>Tipo_IntervencaoHerbal knowledge assessment</t>
         </is>
       </c>
       <c r="C23">
-        <v>1.284375467897118</v>
+        <v>-0.1823219999999448</v>
       </c>
       <c r="D23">
-        <v>0.3666299837127522</v>
+        <v>2.041737101810139E-08</v>
       </c>
       <c r="E23">
-        <v>0.0597883149788383</v>
+        <v>4.213247225967935E-09</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -917,22 +917,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional weather knowledge</t>
+          <t>Tipo_IntervencaoIndigenous knowledge transmission</t>
         </is>
       </c>
       <c r="C24">
-        <v>0.4054659999998182</v>
+        <v>-0.1823219999999763</v>
       </c>
       <c r="D24">
-        <v>5.545266480532413E-08</v>
+        <v>5.250736891622865E-08</v>
       </c>
       <c r="E24">
-        <v>8.706590156875437E-08</v>
+        <v>7.808885961165449E-15</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -941,22 +941,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoBiocultural conservation</t>
+          <t>Tipo_IntervencaoIndigenous storytelling review</t>
         </is>
       </c>
       <c r="C25">
-        <v>0.4159000113255027</v>
+        <v>-0.1823219999999813</v>
       </c>
       <c r="D25">
-        <v>0.04071626846706578</v>
+        <v>4.755584580042266E-08</v>
       </c>
       <c r="E25">
-        <v>0.02204501357862631</v>
+        <v>6.024953213973901E-15</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -965,22 +965,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoEcological knowledge indicator</t>
+          <t>Tipo_IntervencaoPost-disaster food security</t>
         </is>
       </c>
       <c r="C26">
-        <v>-0.9190359999999975</v>
+        <v>-0.1524690368502686</v>
       </c>
       <c r="D26">
-        <v>9.858574371191432E-08</v>
+        <v>5.66275985505266E-09</v>
       </c>
       <c r="E26">
-        <v>6.829072388955097E-08</v>
+        <v>6.749780097412161E-09</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -989,22 +989,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoSacred grove conservation</t>
+          <t>Tipo_IntervencaoSeed system assessment</t>
         </is>
       </c>
       <c r="C27">
-        <v>1.496113248204239</v>
+        <v>-0.0501560024142495</v>
       </c>
       <c r="D27">
-        <v>0.2033511383872229</v>
+        <v>8.993622513450309E-08</v>
       </c>
       <c r="E27">
-        <v>0.01375945420482391</v>
+        <v>1.594242040586114E-16</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1013,22 +1013,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoBiocultural landscape assessment</t>
+          <t>RegiaoAmerica do Sul</t>
         </is>
       </c>
       <c r="C28">
-        <v>-0.4054660000000704</v>
+        <v>3.183065810929977E-15</v>
       </c>
       <c r="D28">
-        <v>1.297501283910137E-08</v>
+        <v>5.821254098248287E-16</v>
       </c>
       <c r="E28">
-        <v>2.037199104253393E-08</v>
+        <v>0.03606973199690495</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1037,22 +1037,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoEthnobotanical assessment</t>
+          <t>Tipo_IntervencaoBiocultural conservation</t>
         </is>
       </c>
       <c r="C29">
-        <v>-0.1823220000000632</v>
+        <v>0.4159000113255091</v>
       </c>
       <c r="D29">
-        <v>1.337433710734009E-08</v>
+        <v>0.04071626846697345</v>
       </c>
       <c r="E29">
-        <v>4.669961630959654E-08</v>
+        <v>0.05900636413761144</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1061,22 +1061,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoSacred grove conservation</t>
+          <t>Tipo_IntervencaoEcological knowledge indicator</t>
         </is>
       </c>
       <c r="C30">
-        <v>1.406656672439215</v>
+        <v>-0.9190359999999899</v>
       </c>
       <c r="D30">
-        <v>0.09861685207393696</v>
+        <v>3.98884267384894E-08</v>
       </c>
       <c r="E30">
-        <v>0.001126522168524515</v>
+        <v>5.38285878341703E-12</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1085,22 +1085,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional flood knowledge</t>
+          <t>Tipo_IntervencaoEthnobotanical assessment</t>
         </is>
       </c>
       <c r="C31">
-        <v>0.4552160375417167</v>
+        <v>-0.6931469999999886</v>
       </c>
       <c r="D31">
-        <v>0.07684727571339657</v>
+        <v>2.780692619870031E-08</v>
       </c>
       <c r="E31">
-        <v>0.01999928005606436</v>
+        <v>1.23728818500874E-13</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1109,22 +1109,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
+          <t>Tipo_IntervencaoSacred grove conservation</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.6433979624573464</v>
+        <v>1.496113248204263</v>
       </c>
       <c r="D32">
-        <v>0.07684727571335395</v>
+        <v>0.2033511383872581</v>
       </c>
       <c r="E32">
-        <v>0.009348025067925468</v>
+        <v>0.04983050880038719</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1133,22 +1133,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RegiaoAsia</t>
+          <t>Tipo_IntervencaoSeed system assessment</t>
         </is>
       </c>
       <c r="C33">
-        <v>-0.3557159624576263</v>
+        <v>0.8659998902642483</v>
       </c>
       <c r="D33">
-        <v>0.07684727571346435</v>
+        <v>4.02079070003682E-08</v>
       </c>
       <c r="E33">
-        <v>0.09480214236528751</v>
+        <v>5.54998629132899E-11</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1157,25 +1157,1465 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>RegiaoAmerica do Sul</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>-3.163294273238972E-15</v>
+      </c>
+      <c r="D34">
+        <v>4.973329232734548E-16</v>
+      </c>
+      <c r="E34">
+        <v>0.0151668774108879</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgrobiodiversity assessment</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>-0.4054660000000088</v>
+      </c>
+      <c r="D35">
+        <v>1.590508755611532E-08</v>
+      </c>
+      <c r="E35">
+        <v>2.168474281861961E-15</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgroforestry assessment</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>-0.3693764514751506</v>
+      </c>
+      <c r="D36">
+        <v>0.06994365617217911</v>
+      </c>
+      <c r="E36">
+        <v>0.02858370504914192</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgroforestry management</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>-0.117784000000019</v>
+      </c>
+      <c r="D37">
+        <v>4.435039344542864E-08</v>
+      </c>
+      <c r="E37">
+        <v>2.397128419788388E-07</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiocultural landscape assessment</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>-0.8109319999999717</v>
+      </c>
+      <c r="D38">
+        <v>1.191947804086591E-08</v>
+      </c>
+      <c r="E38">
+        <v>9.357351044374503E-09</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoClimate adaptation assessment</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>0.1470910000000303</v>
+      </c>
+      <c r="D39">
+        <v>5.89342056991994E-08</v>
+      </c>
+      <c r="E39">
+        <v>9.818303653358912E-08</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoEcological knowledge indicator</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>-0.03482800000001911</v>
+      </c>
+      <c r="D40">
+        <v>4.435039344542864E-08</v>
+      </c>
+      <c r="E40">
+        <v>8.106792632252986E-07</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoEthnobotanical assessment</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>-0.5877880000000089</v>
+      </c>
+      <c r="D41">
+        <v>1.650964015348668E-08</v>
+      </c>
+      <c r="E41">
+        <v>1.788121458141917E-08</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoFarmer perception survey</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>-0.4054659999999628</v>
+      </c>
+      <c r="D42">
+        <v>5.893420569919939E-08</v>
+      </c>
+      <c r="E42">
+        <v>9.253224836827677E-08</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoHerbal knowledge assessment</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>-0.1823219999999625</v>
+      </c>
+      <c r="D43">
+        <v>5.845616832582532E-08</v>
+      </c>
+      <c r="E43">
+        <v>2.041133410837656E-07</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoHome garden knowledge transmission</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>-0.4882879249157345</v>
+      </c>
+      <c r="D44">
+        <v>0.09861685207393911</v>
+      </c>
+      <c r="E44">
+        <v>0.0171643535113959</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoIndigenous knowledge transmission</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>-0.1177840000000386</v>
+      </c>
+      <c r="D45">
+        <v>4.369770454286324E-08</v>
+      </c>
+      <c r="E45">
+        <v>2.3618507368618E-07</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoIndigenous storytelling review</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>-0.8109320000000204</v>
+      </c>
+      <c r="D46">
+        <v>4.350129541861044E-08</v>
+      </c>
+      <c r="E46">
+        <v>3.415056353318153E-08</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoLandscape ethnoecology</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>-0.4054660000000089</v>
+      </c>
+      <c r="D47">
+        <v>1.590508755611532E-08</v>
+      </c>
+      <c r="E47">
+        <v>2.497248405405227E-08</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoMedicinal plant survey</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>-0.305965924915723</v>
+      </c>
+      <c r="D48">
+        <v>0.09861685207394058</v>
+      </c>
+      <c r="E48">
+        <v>0.05573233934794738</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoOn-farm conservation</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>-0.5003021598995259</v>
+      </c>
+      <c r="D49">
+        <v>0.0949152090120424</v>
+      </c>
+      <c r="E49">
+        <v>0.0988926172145002</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoPost-disaster food security</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>0.1093204736679043</v>
+      </c>
+      <c r="D50">
+        <v>3.788128166567605E-08</v>
+      </c>
+      <c r="E50">
+        <v>2.20598869560828E-07</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSacred grove conservation</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>1.001190672439407</v>
+      </c>
+      <c r="D51">
+        <v>0.09861685207393864</v>
+      </c>
+      <c r="E51">
+        <v>0.002363121201091716</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSeed system assessment</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>-0.4907934081473421</v>
+      </c>
+      <c r="D52">
+        <v>4.435383470077377E-08</v>
+      </c>
+      <c r="E52">
+        <v>5.753241115732121E-08</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSoil conservation assessment</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>-0.6152179999999764</v>
+      </c>
+      <c r="D53">
+        <v>3.788128166567606E-08</v>
+      </c>
+      <c r="E53">
+        <v>3.919906912833469E-08</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional beekeeping</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>-0.810931999999989</v>
+      </c>
+      <c r="D54">
+        <v>4.268491348302239E-08</v>
+      </c>
+      <c r="E54">
+        <v>3.350966530497249E-08</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional knowledge erosion</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>0.2379319624578659</v>
+      </c>
+      <c r="D55">
+        <v>0.07684727571347395</v>
+      </c>
+      <c r="E55">
+        <v>0.07780557323203485</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RegiaoAsia</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>-0.3557159624578889</v>
+      </c>
+      <c r="D56">
+        <v>0.07684727571346041</v>
+      </c>
+      <c r="E56">
+        <v>0.09480214236519727</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Tipo_ComunidadeRural</t>
         </is>
       </c>
-      <c r="C34">
-        <v>0.3059659249153711</v>
-      </c>
-      <c r="D34">
-        <v>0.09861685207388907</v>
-      </c>
-      <c r="E34">
-        <v>0.09142004126279575</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+      <c r="C57">
+        <v>0.3059659249157254</v>
+      </c>
+      <c r="D57">
+        <v>0.09861685207393255</v>
+      </c>
+      <c r="E57">
+        <v>0.09142004126268299</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiocultural diversity assessment</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>5.363654009336764E-15</v>
+      </c>
+      <c r="D58">
+        <v>1.705734729876944E-15</v>
+      </c>
+      <c r="E58">
+        <v>0.03966891706460101</v>
+      </c>
+      <c r="F58">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSeed system assessment</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>8.890942839668859E-15</v>
+      </c>
+      <c r="D59">
+        <v>2.145469470013913E-15</v>
+      </c>
+      <c r="E59">
+        <v>0.02259372425307902</v>
+      </c>
+      <c r="F59">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional flood knowledge</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>7.77285436015518E-15</v>
+      </c>
+      <c r="D60">
+        <v>9.342281724058979E-16</v>
+      </c>
+      <c r="E60">
+        <v>0.04535389621101703</v>
+      </c>
+      <c r="F60">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional weather knowledge</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>9.716067950193974E-15</v>
+      </c>
+      <c r="D61">
+        <v>2.642396303534902E-15</v>
+      </c>
+      <c r="E61">
+        <v>0.03416004791149953</v>
+      </c>
+      <c r="F61">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoVulnerability assessment</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>9.716067950193974E-15</v>
+      </c>
+      <c r="D62">
+        <v>2.642396303534902E-15</v>
+      </c>
+      <c r="E62">
+        <v>0.03408775084620243</v>
+      </c>
+      <c r="F62">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgrobiodiversity assessment</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>-0.1823219999999958</v>
+      </c>
+      <c r="D63">
+        <v>2.923067742982511E-16</v>
+      </c>
+      <c r="E63">
+        <v>1.02065725537936E-15</v>
+      </c>
+      <c r="F63">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgroforestry assessment</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>-0.1823219999999516</v>
+      </c>
+      <c r="D64">
+        <v>4.752263773908058E-08</v>
+      </c>
+      <c r="E64">
+        <v>2.028198519834202E-12</v>
+      </c>
+      <c r="F64">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoAgroforestry management</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>-0.1823219999999486</v>
+      </c>
+      <c r="D65">
+        <v>4.752263773908049E-08</v>
+      </c>
+      <c r="E65">
+        <v>1.801281164886534E-07</v>
+      </c>
+      <c r="F65">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiocultural conservation</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>-0.1823219999999499</v>
+      </c>
+      <c r="D66">
+        <v>4.752263773908056E-08</v>
+      </c>
+      <c r="E66">
+        <v>2.072697275004457E-12</v>
+      </c>
+      <c r="F66">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiocultural diversity assessment</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>-0.1823219999999481</v>
+      </c>
+      <c r="D67">
+        <v>4.752263773908049E-08</v>
+      </c>
+      <c r="E67">
+        <v>1.793195456525582E-07</v>
+      </c>
+      <c r="F67">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiocultural landscape assessment</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>-0.1823219999999957</v>
+      </c>
+      <c r="D68">
+        <v>1.687633948378982E-16</v>
+      </c>
+      <c r="E68">
+        <v>7.973868315494368E-16</v>
+      </c>
+      <c r="F68">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBionic architecture assessment</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>-0.1823219999999243</v>
+      </c>
+      <c r="D69">
+        <v>1.033036025463047E-07</v>
+      </c>
+      <c r="E69">
+        <v>8.935599134647994E-10</v>
+      </c>
+      <c r="F69">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoBiosphere reserve assessment</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>-0.1823219999999506</v>
+      </c>
+      <c r="D70">
+        <v>9.172367852069499E-08</v>
+      </c>
+      <c r="E70">
+        <v>4.793516448317718E-07</v>
+      </c>
+      <c r="F70">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoClimate adaptation assessment</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>0.1875210000000166</v>
+      </c>
+      <c r="D71">
+        <v>1.03303602546328E-07</v>
+      </c>
+      <c r="E71">
+        <v>3.849626273686108E-07</v>
+      </c>
+      <c r="F71">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoCultural species assessment</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>-0.1823219999999504</v>
+      </c>
+      <c r="D72">
+        <v>4.752263773908047E-08</v>
+      </c>
+      <c r="E72">
+        <v>6.581121452184386E-13</v>
+      </c>
+      <c r="F72">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoEcological knowledge indicator</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>-0.1823219999999481</v>
+      </c>
+      <c r="D73">
+        <v>4.752263773908049E-08</v>
+      </c>
+      <c r="E73">
+        <v>1.793195456525582E-07</v>
+      </c>
+      <c r="F73">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoEthnobotanical assessment</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>-0.1823219999999956</v>
+      </c>
+      <c r="D74">
+        <v>2.066921022997324E-16</v>
+      </c>
+      <c r="E74">
+        <v>1.035049637732463E-15</v>
+      </c>
+      <c r="F74">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoEthnobotanical survey</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>-0.1823219999999212</v>
+      </c>
+      <c r="D75">
+        <v>1.033036025463052E-07</v>
+      </c>
+      <c r="E75">
+        <v>5.617870124795057E-07</v>
+      </c>
+      <c r="F75">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoFarmer perception survey</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>-0.1823219999999038</v>
+      </c>
+      <c r="D76">
+        <v>1.033036025462936E-07</v>
+      </c>
+      <c r="E76">
+        <v>4.026947017839028E-07</v>
+      </c>
+      <c r="F76">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoFlora checklist</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>-0.1823219999999955</v>
+      </c>
+      <c r="D77">
+        <v>1.193337409204018E-16</v>
+      </c>
+      <c r="E77">
+        <v>4.283989108925215E-31</v>
+      </c>
+      <c r="F77">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoHerbal knowledge assessment</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>-0.1823219999999031</v>
+      </c>
+      <c r="D78">
+        <v>1.033036025462936E-07</v>
+      </c>
+      <c r="E78">
+        <v>4.026947017839042E-07</v>
+      </c>
+      <c r="F78">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoHome garden knowledge transmission</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>-0.1823219999999502</v>
+      </c>
+      <c r="D79">
+        <v>4.752263773908051E-08</v>
+      </c>
+      <c r="E79">
+        <v>6.689115159823281E-13</v>
+      </c>
+      <c r="F79">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoIndigenous knowledge transmission</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>-0.1823219999999507</v>
+      </c>
+      <c r="D80">
+        <v>4.752263773908049E-08</v>
+      </c>
+      <c r="E80">
+        <v>1.793195456525557E-07</v>
+      </c>
+      <c r="F80">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoIndigenous storytelling review</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>-0.18232199999995</v>
+      </c>
+      <c r="D81">
+        <v>4.752263773908057E-08</v>
+      </c>
+      <c r="E81">
+        <v>1.788838983041404E-07</v>
+      </c>
+      <c r="F81">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoLand sharing assessment</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>-0.1823219999999038</v>
+      </c>
+      <c r="D82">
+        <v>1.033036025462936E-07</v>
+      </c>
+      <c r="E82">
+        <v>4.026947017839028E-07</v>
+      </c>
+      <c r="F82">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoLandscape ethnoecology</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>-0.1823219999999956</v>
+      </c>
+      <c r="D83">
+        <v>2.066921022999298E-16</v>
+      </c>
+      <c r="E83">
+        <v>9.762747242732468E-16</v>
+      </c>
+      <c r="F83">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoMedicinal plant survey</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>-0.1823219999999958</v>
+      </c>
+      <c r="D84">
+        <v>1.687633948397464E-16</v>
+      </c>
+      <c r="E84">
+        <v>8.567978215961453E-31</v>
+      </c>
+      <c r="F84">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoNature-connectedness assessment</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>-0.1823219999999038</v>
+      </c>
+      <c r="D85">
+        <v>1.033036025462936E-07</v>
+      </c>
+      <c r="E85">
+        <v>4.026947017839028E-07</v>
+      </c>
+      <c r="F85">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoOn-farm conservation</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>-0.1823219999999481</v>
+      </c>
+      <c r="D86">
+        <v>9.172367852069489E-08</v>
+      </c>
+      <c r="E86">
+        <v>1.301881678085174E-09</v>
+      </c>
+      <c r="F86">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoPost-disaster food security</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>0.2876820000000969</v>
+      </c>
+      <c r="D87">
+        <v>1.033036025462936E-07</v>
+      </c>
+      <c r="E87">
+        <v>2.577380440886607E-07</v>
+      </c>
+      <c r="F87">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSacred grove conservation</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>-0.1823219999999504</v>
+      </c>
+      <c r="D88">
+        <v>4.752263773908047E-08</v>
+      </c>
+      <c r="E88">
+        <v>6.581121452184386E-13</v>
+      </c>
+      <c r="F88">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSeed system assessment</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>-0.1823219999999502</v>
+      </c>
+      <c r="D89">
+        <v>4.752263773908046E-08</v>
+      </c>
+      <c r="E89">
+        <v>1.817859286657542E-07</v>
+      </c>
+      <c r="F89">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSocial-ecological monitoring</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>-0.1823219999999447</v>
+      </c>
+      <c r="D90">
+        <v>9.17236785206949E-08</v>
+      </c>
+      <c r="E90">
+        <v>4.778479370556963E-07</v>
+      </c>
+      <c r="F90">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoSoil conservation assessment</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>-0.1823219999999055</v>
+      </c>
+      <c r="D91">
+        <v>1.033036025462935E-07</v>
+      </c>
+      <c r="E91">
+        <v>4.071246459424172E-07</v>
+      </c>
+      <c r="F91">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional beekeeping</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>-0.1823219999999497</v>
+      </c>
+      <c r="D92">
+        <v>4.752263773908045E-08</v>
+      </c>
+      <c r="E92">
+        <v>1.799724943124664E-07</v>
+      </c>
+      <c r="F92">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional flood knowledge</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>-0.4054659999999209</v>
+      </c>
+      <c r="D93">
+        <v>1.033036025463047E-07</v>
+      </c>
+      <c r="E93">
+        <v>2.816891795722343E-10</v>
+      </c>
+      <c r="F93">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tipo_IntervencaoTraditional weather knowledge</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>-0.4054659999999009</v>
+      </c>
+      <c r="D94">
+        <v>1.033036025462935E-07</v>
+      </c>
+      <c r="E94">
+        <v>1.822239275290099E-07</v>
+      </c>
+      <c r="F94">
+        <v>0.233</v>
       </c>
     </row>
   </sheetData>
